--- a/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
+++ b/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hardi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2360B10-C035-4E5A-8DBF-67E70306D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F612C0-CF5F-4DDC-92AE-CE76B263A026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="10905" xr2:uid="{1541C50B-7FC4-48E3-8867-20EDB5C9B5A2}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15825" xr2:uid="{1541C50B-7FC4-48E3-8867-20EDB5C9B5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Distributor</t>
   </si>
@@ -103,6 +114,12 @@
   </si>
   <si>
     <t>RES SMD 100K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 10V X5R 0402</t>
+  </si>
+  <si>
+    <t>CC0402MRX5R6BB106</t>
   </si>
 </sst>
 </file>
@@ -110,8 +127,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -142,10 +159,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5575892C-D31C-4E56-ADA6-4A82E30382AE}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -554,14 +574,14 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E10" si="0">D3*5</f>
+        <f t="shared" ref="E3:E11" si="0">D3*5</f>
         <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>2.46</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G10" si="1">E3*F3</f>
+        <f t="shared" ref="G3:G11" si="1">E3*F3</f>
         <v>12.3</v>
       </c>
     </row>
@@ -665,79 +685,110 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f>D8*5</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="G8" s="2">
+        <f>E8*F8</f>
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F9" s="2">
         <v>0.08</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F10" s="2">
         <v>0.1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G10" s="2">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F11" s="2">
         <v>0.1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="2">
         <f t="shared" si="1"/>
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="2">
+        <f>SUM(G2:G11)</f>
+        <v>62.349999999999994</v>
       </c>
     </row>
   </sheetData>

--- a/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
+++ b/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hardi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F612C0-CF5F-4DDC-92AE-CE76B263A026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CACBFE7-9555-4044-BDF6-A1CDE234C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15825" xr2:uid="{1541C50B-7FC4-48E3-8867-20EDB5C9B5A2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Distributor</t>
   </si>
@@ -120,17 +120,31 @@
   </si>
   <si>
     <t>CC0402MRX5R6BB106</t>
+  </si>
+  <si>
+    <t>CAP CER 0402 10PF 10V ULTRA STAB</t>
+  </si>
+  <si>
+    <t>C0402C100K8HACAUTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,18 +170,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -500,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5575892C-D31C-4E56-ADA6-4A82E30382AE}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -574,14 +591,14 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E11" si="0">D3*5</f>
+        <f t="shared" ref="E3:E12" si="0">D3*5</f>
         <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>2.46</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G11" si="1">E3*F3</f>
+        <f t="shared" ref="G3:G12" si="1">E3*F3</f>
         <v>12.3</v>
       </c>
     </row>
@@ -671,18 +688,18 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
         <v>0.1</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -786,8 +803,33 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.1</v>
+      </c>
       <c r="G12" s="2">
-        <f>SUM(G2:G11)</f>
+        <f>E12*F12</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="4">
+        <f>SUM(G2:G12)</f>
         <v>62.349999999999994</v>
       </c>
     </row>

--- a/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
+++ b/Byte the Sky/inspireflybytetheskysmallboard/ByteTheSkye_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hardi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CACBFE7-9555-4044-BDF6-A1CDE234C7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F898562E-3CDB-4B80-9622-A0ECC4EE9F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="15825" xr2:uid="{1541C50B-7FC4-48E3-8867-20EDB5C9B5A2}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="10500" xr2:uid="{1541C50B-7FC4-48E3-8867-20EDB5C9B5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>Distributor</t>
   </si>
@@ -126,16 +126,23 @@
   </si>
   <si>
     <t>C0402C100K8HACAUTO</t>
+  </si>
+  <si>
+    <t>Etsy - https://www.etsy.com/listing/1186384627/multiple-size-630nm-dark-red-glass?gpla=1&amp;gao=1&amp;</t>
+  </si>
+  <si>
+    <t>Multiple Size 630nm Dark Red Glass Optical Filter HB630 RG630</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -172,16 +179,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -517,19 +525,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5575892C-D31C-4E56-ADA6-4A82E30382AE}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="7" max="7" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -577,7 +585,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -591,18 +599,18 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E12" si="0">D3*5</f>
+        <f t="shared" ref="E3:E13" si="0">D3*5</f>
         <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>2.46</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G12" si="1">E3*F3</f>
+        <f t="shared" ref="G3:G11" si="1">E3*F3</f>
         <v>12.3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -627,7 +635,7 @@
         <v>11.200000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -652,7 +660,7 @@
         <v>17.05</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -677,7 +685,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -702,7 +710,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -727,7 +735,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -752,7 +760,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -777,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -802,7 +810,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -827,10 +835,32 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f>D13*3</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>6</v>
+      </c>
       <c r="G13" s="4">
-        <f>SUM(G2:G12)</f>
-        <v>62.349999999999994</v>
+        <f>E13*F13+18</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14" s="5">
+        <f>SUM(G2:G13)</f>
+        <v>98.35</v>
       </c>
     </row>
   </sheetData>
